--- a/insumos_movimientos.xlsx
+++ b/insumos_movimientos.xlsx
@@ -1348,7 +1348,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1397,26 +1397,38 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>ALCOHOL GEL 500 ML</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>50</v>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>-89</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>-34</v>
+          <t>AMONIO GALON</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1433,7 +1445,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
@@ -1482,26 +1494,38 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>CEPILLO FORMA GUSANO MATERIAL CERDA</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="n">
-        <v>45</v>
-      </c>
-      <c r="C2" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D2" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="F2" s="8" t="n">
-        <v>-5</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>36</v>
+          <t>BOLSA 50 LBS TRANSPARENTE</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>-5.0</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
       </c>
     </row>
   </sheetData>
